--- a/InputData/dist-heat/HDL/na-Heat Distribution Losses.xlsx
+++ b/InputData/dist-heat/HDL/na-Heat Distribution Losses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Liya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EPS in github\Github China\eps-china2019-smart-trans\InputData\dist-heat\HDL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C684BB2E-0859-4203-954E-23017962578D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23058FC6-6F9E-4495-8016-E1864E0494E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7FE0438B-EB0E-443A-8B0B-C67805A5FF58}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="27045" windowHeight="13485" activeTab="2" xr2:uid="{7FE0438B-EB0E-443A-8B0B-C67805A5FF58}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>HDL Heat Distribution Losses</t>
   </si>
@@ -82,6 +82,14 @@
   </si>
   <si>
     <t>Page 5, table 2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明：能源统计年鉴中热力的生产和消费量几乎一致，在NCSC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目中，认为Heat Distribution Loss为0</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -89,7 +97,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +136,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -150,7 +166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -161,6 +177,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -322,9 +342,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -362,7 +382,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -468,7 +488,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -610,7 +630,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -618,20 +638,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FBE8349-D73E-42FD-BD61-5E87CB115BAE}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.265625" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="2"/>
-    <col min="7" max="7" width="10.3984375" customWidth="1"/>
+    <col min="1" max="1" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="2"/>
+    <col min="7" max="7" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -639,45 +659,63 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>2022</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -693,26 +731,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48831E50-4931-41B4-97B3-85E9488A84AB}">
   <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.265625" customWidth="1"/>
-    <col min="2" max="2" width="9.06640625" style="2"/>
-    <col min="7" max="7" width="10.3984375" customWidth="1"/>
+    <col min="1" max="1" width="17.25" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="2"/>
+    <col min="7" max="7" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H34" t="s">
         <v>5</v>
       </c>
@@ -731,13 +769,13 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.265625" customWidth="1"/>
-    <col min="2" max="33" width="8.3984375" customWidth="1"/>
+    <col min="1" max="1" width="30.25" customWidth="1"/>
+    <col min="2" max="33" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,170 +906,135 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.19500000000000001</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <f>$H2</f>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:AQ2" si="0">$H2</f>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
